--- a/branches/pt/CodeSystem-pt-ingredient-item-cs.xlsx
+++ b/branches/pt/CodeSystem-pt-ingredient-item-cs.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/CodeSystem/lymphnodes</t>
+    <t>http://medigree.net/fhir/mpd5/CodeSystem/pt-ingredient-item-cs</t>
   </si>
   <si>
     <t>Version</t>
@@ -37,7 +37,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>PTINGITEMCS</t>
+    <t>PTSubstanceCS</t>
   </si>
   <si>
     <t>Title</t>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-24T21:33:25+00:00</t>
+    <t>2022-08-29T19:31:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
